--- a/Uploads/import_mahasiswa_1750151694.xlsx
+++ b/Uploads/import_mahasiswa_1750151694.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bendaharap2s3/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/MAMP/htdocs/siakad/Uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD61FED-15EE-5C48-8CF4-B55DCF855421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28E5AF9-FF0D-3145-B2C9-11BA05419C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{BFFF2D5A-37DC-3F49-83B3-58E8C14DD6C9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>NIS</t>
   </si>
@@ -93,6 +93,21 @@
   </si>
   <si>
     <t>AKTIF</t>
+  </si>
+  <si>
+    <t>ni334</t>
+  </si>
+  <si>
+    <t>Sinaruddin</t>
+  </si>
+  <si>
+    <t>Kupang</t>
+  </si>
+  <si>
+    <t>Sukorejo</t>
+  </si>
+  <si>
+    <t>kupang@co.ud</t>
   </si>
 </sst>
 </file>
@@ -476,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C4ACAB7-A5E6-0D42-AA2E-D7855D0DD929}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -557,9 +572,45 @@
         <v>18</v>
       </c>
     </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>990923</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1">
+        <v>36777</v>
+      </c>
+      <c r="F3">
+        <v>812321343</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{09887180-E5E1-DB41-8710-FF3B03E3A30D}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{3049D693-884A-AB49-863E-34D744A01864}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
